--- a/tame_output/ON/bt/strategyON_20240229.xlsx
+++ b/tame_output/ON/bt/strategyON_20240229.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-45.6%</t>
+          <t>-45.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.7%</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>128.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
     </row>
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>1.159241507300391</v>
+        <v>1.161194479453429</v>
       </c>
       <c r="E1888" t="n">
-        <v>3.642662873010088</v>
+        <v>3.643444061871303</v>
       </c>
       <c r="F1888" t="n">
-        <v>2.445067374850911</v>
+        <v>2.447020347003948</v>
       </c>
       <c r="G1888" t="n">
-        <v>4.646363119314226</v>
+        <v>4.647534902606048</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240229.xlsx
+++ b/tame_output/ON/bt/strategyON_20240229.xlsx
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>1.161194479453429</v>
+        <v>1.1605222206186</v>
       </c>
       <c r="E1888" t="n">
-        <v>3.643444061871303</v>
+        <v>3.643175158337372</v>
       </c>
       <c r="F1888" t="n">
-        <v>2.447020347003948</v>
+        <v>2.44634808816912</v>
       </c>
       <c r="G1888" t="n">
-        <v>4.647534902606048</v>
+        <v>4.647131547305151</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240229.xlsx
+++ b/tame_output/ON/bt/strategyON_20240229.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>442.1%</t>
+          <t>444.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-45.5%</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-19.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,32 +1318,32 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>2.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.6%</t>
+          <t>128.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>122.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
     </row>
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>1.1605222206186</v>
+        <v>0.9789526385106422</v>
       </c>
       <c r="E1888" t="n">
-        <v>3.643175158337372</v>
+        <v>3.570547325494188</v>
       </c>
       <c r="F1888" t="n">
-        <v>2.44634808816912</v>
+        <v>2.264778506061162</v>
       </c>
       <c r="G1888" t="n">
-        <v>4.647131547305151</v>
+        <v>4.538189798040376</v>
       </c>
     </row>
   </sheetData>
